--- a/survey_templates/032_child_protection_awareness_survey--survey_templates.xlsx
+++ b/survey_templates/032_child_protection_awareness_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_fully_aware',_'value':_true}</t>
+          <t>yes_-_fully_aware</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Fully Aware', 'value': True}</t>
+          <t>Yes - Fully Aware</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_not_aware',_'value':_false}</t>
+          <t>no_-_not_aware</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'No - Not Aware', 'value': False}</t>
+          <t>No - Not Aware</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'unsure_-_need_information',_'value':_'unsure'}</t>
+          <t>unsure_-_need_information</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Unsure - Need Information', 'value': 'unsure'}</t>
+          <t>Unsure - Need Information</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_i_know_the_procedure',_'value':_true}</t>
+          <t>yes_-_i_know_the_procedure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - I know the procedure', 'value': True}</t>
+          <t>Yes - I know the procedure</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_i_am_unsure',_'value':_false}</t>
+          <t>no_-_i_am_unsure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'No - I am unsure', 'value': False}</t>
+          <t>No - I am unsure</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'within_the_last_1_year',_'value':_'recent'}</t>
+          <t>within_the_last_1_year</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Within the last 1 year', 'value': 'recent'}</t>
+          <t>Within the last 1 year</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'1_to_3_years_ago',_'value':_'mid'}</t>
+          <t>1_to_3_years_ago</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '1 to 3 years ago', 'value': 'mid'}</t>
+          <t>1 to 3 years ago</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'over_3_years_ago',_'value':_'old'}</t>
+          <t>over_3_years_ago</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Over 3 years ago', 'value': 'old'}</t>
+          <t>Over 3 years ago</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'never_had_training',_'value':_'never'}</t>
+          <t>never_had_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Never had training', 'value': 'never'}</t>
+          <t>Never had training</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_clearly_posted',_'value':_true}</t>
+          <t>yes_-_clearly_posted</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Clearly Posted', 'value': True}</t>
+          <t>Yes - Clearly Posted</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_hard_to_find',_'value':_false}</t>
+          <t>no_-_hard_to_find</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'No - Hard to Find', 'value': False}</t>
+          <t>No - Hard to Find</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'strongly_agree',_'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Strongly Agree', 'value': 'strongly_agree'}</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'agree',_'value':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Agree', 'value': 'agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'disagree',_'value':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree', 'value': 'disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'online_training_modules',_'value':_'online'}</t>
+          <t>online_training_modules</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Online Training Modules', 'value': 'online'}</t>
+          <t>Online Training Modules</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'in-person_workshops',_'value':_'workshops'}</t>
+          <t>in-person_workshops</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'In-person Workshops', 'value': 'workshops'}</t>
+          <t>In-person Workshops</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'print_handouts_and_guides',_'value':_'handouts'}</t>
+          <t>print_handouts_and_guides</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Print Handouts and Guides', 'value': 'handouts'}</t>
+          <t>Print Handouts and Guides</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'educational_videos',_'value':_'videos'}</t>
+          <t>educational_videos</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Educational Videos', 'value': 'videos'}</t>
+          <t>Educational Videos</t>
         </is>
       </c>
     </row>
